--- a/Bartlett__2003/Bartlett__2003_registry_rows.xlsx
+++ b/Bartlett__2003/Bartlett__2003_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R28168c80c9fc4517"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R330f7420d8764961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R97d60bae1d704590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rb1e92341b2c14d02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R7ab3a23be88b49e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rb039cce3f68b4230"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Gibbon play time and social activity budgets</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Figure 4: Gibbon grooming, play and contact by age/sex class</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — resolve citation and compilation coverage
@@ -350,13 +350,47 @@
         <x:v>Francesca Hicks dissertation: Table 1 note, Behavioural Data and References (local final draft). Fran reference list Bartlett &amp; Fanning entry; Kerney Online Resource 1 needs checking.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 9 / printed p. 247. Percentages of SOCIAL activity allocated to each behaviour, not percentages of all activity. The dissertation citation mismatch and Kerney overlap hold remain unresolved.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/2426206476/Bartlett-2003-Intragroup and intergroup social.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="180" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>Bartlett__2003</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="str">
+        <x:v>Gibbon play time and social activity budgets</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="str">
+        <x:v>Figure 5: Monthly variation in gibbon play and grooming activity</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="str">
+        <x:v>HOLD — resolve citation and compilation coverage
+Fran names Bartlett 2003, but her bibliography lists Bartlett &amp; Fanning on preterm human infants. This gibbon paper was an inferred correction, not a verified dissertation source. Resolve against Kerney Online Resource 1 before any extraction.
+Original source note: Primary-source review. Verify age classes, denominators and exact table. Check overlap with Kerney 2017. This is the gibbon paper, not the unrelated Bartlett and Fanning infant motor-development paper.</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="str">
+        <x:v>https://doi.org/10.1023/A:1023088814263</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="str">
+        <x:v>Possible intended source; dissertation citation mismatch</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>Francesca Hicks dissertation: Table 1 note, Behavioural Data and References (local final draft). Fran reference list Bartlett &amp; Fanning entry; Kerney Online Resource 1 needs checking.</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="str">
+        <x:v>Verified in EndNote full text — PDF p. 9 / printed p. 247. Monthly percentage of activity; preserve month, sampling and denominator. Do not combine with Figure 4 without a justified conversion. Check Kerney coverage before extraction.</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="str">
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="str">
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/2426206476/Bartlett-2003-Intragroup and intergroup social.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +542,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Bartlett, T. Q. (2003). Intragroup and intergroup social interactions in white-handed gibbons. International Journal of Primatology, 24(2), 239–259. https://doi.org/10.1023/A:1023088814263</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Figure 4</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +561,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Possible intended source; dissertation citation mismatch. Planned folder: Bartlett__2003. Target: Source tables / results to select. Primary-source review. Verify age classes, denominators and exact table. Check overlap with Kerney 2017. This is the gibbon paper, not the unrelated Bartlett and Fanning infant motor-development paper.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 9 / printed p. 247. Percentages of SOCIAL activity allocated to each behaviour, not percentages of all activity. The dissertation citation mismatch and Kerney overlap hold remain unresolved. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/2426206476/Bartlett-2003-Intragroup and intergroup social.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — resolve citation and compilation coverage</x:v>
@@ -550,7 +586,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Gibbon play time and social activity budgets</x:v>
+        <x:v>Gibbon grooming, play and contact by age/sex class</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -570,6 +606,73 @@
         <x:v>Fran names Bartlett 2003, but her bibliography lists Bartlett &amp; Fanning on preterm human infants. This gibbon paper was an inferred correction, not a verified dissertation source. Resolve against Kerney Online Resource 1 before any extraction. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
       </x:c>
       <x:c r="AH2" s="3" t="str">
+        <x:v>Pending — no snapshot created</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="200" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>Bartlett, T. Q. (2003). Intragroup and intergroup social interactions in white-handed gibbons. International Journal of Primatology, 24(2), 239–259. https://doi.org/10.1023/A:1023088814263</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3" t="str">
+        <x:v>Figure 5</x:v>
+      </x:c>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
+      <x:c r="I3" s="6"/>
+      <x:c r="J3" s="6"/>
+      <x:c r="K3" s="6"/>
+      <x:c r="L3" s="6"/>
+      <x:c r="M3" s="6"/>
+      <x:c r="N3" s="3" t="str">
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
+      </x:c>
+      <x:c r="O3" s="3" t="str">
+        <x:v>Possible intended source; dissertation citation mismatch. Planned folder: Bartlett__2003. Target: Source tables / results to select. Primary-source review. Verify age classes, denominators and exact table. Check overlap with Kerney 2017. This is the gibbon paper, not the unrelated Bartlett and Fanning infant motor-development paper.
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 9 / printed p. 247. Monthly percentage of activity; preserve month, sampling and denominator. Do not combine with Figure 4 without a justified conversion. Check Kerney coverage before extraction. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/2426206476/Bartlett-2003-Intragroup and intergroup social.pdf</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="str">
+        <x:v>HOLD — resolve citation and compilation coverage</x:v>
+      </x:c>
+      <x:c r="Q3" s="3"/>
+      <x:c r="R3" s="3" t="str">
+        <x:v>https://doi.org/10.1023/A:1023088814263</x:v>
+      </x:c>
+      <x:c r="S3" s="3"/>
+      <x:c r="T3" s="3" t="str">
+        <x:v>Primary-source review. Verify age classes, denominators and exact table. Check overlap with Kerney 2017. This is the gibbon paper, not the unrelated Bartlett and Fanning infant motor-development paper.</x:v>
+      </x:c>
+      <x:c r="U3" s="3"/>
+      <x:c r="V3" s="3" t="str">
+        <x:v>Play</x:v>
+      </x:c>
+      <x:c r="W3" s="3" t="str">
+        <x:v>Primates</x:v>
+      </x:c>
+      <x:c r="X3" s="3" t="str">
+        <x:v>Monthly variation in gibbon play and grooming activity</x:v>
+      </x:c>
+      <x:c r="Y3" s="3"/>
+      <x:c r="Z3" s="3"/>
+      <x:c r="AA3" s="3" t="str">
+        <x:v>Field behavioural observations</x:v>
+      </x:c>
+      <x:c r="AB3" s="3" t="str">
+        <x:v>Behaviour / morphology (verify item)</x:v>
+      </x:c>
+      <x:c r="AC3" s="3"/>
+      <x:c r="AD3" s="3"/>
+      <x:c r="AE3" s="3" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+      <x:c r="AF3" s="3"/>
+      <x:c r="AG3" s="3" t="str">
+        <x:v>Fran names Bartlett 2003, but her bibliography lists Bartlett &amp; Fanning on preterm human infants. This gibbon paper was an inferred correction, not a verified dissertation source. Resolve against Kerney Online Resource 1 before any extraction. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
+      </x:c>
+      <x:c r="AH3" s="3" t="str">
         <x:v>Pending — no snapshot created</x:v>
       </x:c>
     </x:row>
@@ -695,7 +798,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="100" customHeight="1">
@@ -703,7 +806,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -987,13 +1090,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0290B80A-4DC5-49B6-A425-BE16EFB92179}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1D23EBC-D365-4F79-94D2-013F0478B360}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192B5A4-7F62-4BA7-BF57-C826175C8968}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8EB25B4-26F5-405A-8CE1-A3AF8FA2102B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69B077B9-6BFE-4C37-8321-C8E3427F08C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7AB10AC-AD94-47E7-9467-0E20F0FE2F6B}"/>
 </file>